--- a/de_para_orgao.xlsx
+++ b/de_para_orgao.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="138">
   <si>
     <t>para_orgao</t>
   </si>
@@ -449,6 +449,9 @@
   </si>
   <si>
     <t>SEDE</t>
+  </si>
+  <si>
+    <t>DMAES PONTE NOVA</t>
   </si>
 </sst>
 </file>
@@ -1258,7 +1261,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C70"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.85546875" bestFit="1" customWidth="1"/>
@@ -2036,6 +2039,17 @@
         <v>123</v>
       </c>
     </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>137</v>
+      </c>
+      <c r="B71" t="s">
+        <v>133</v>
+      </c>
+      <c r="C71" t="s">
+        <v>133</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C1">
     <sortState ref="A2:C61">

--- a/de_para_orgao.xlsx
+++ b/de_para_orgao.xlsx
@@ -15,7 +15,7 @@
     <sheet name="de_para_orgao" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">de_para_orgao!$A$1:$C$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">de_para_orgao!$A$1:$D$1</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="138">
   <si>
     <t>para_orgao</t>
   </si>
@@ -94,15 +94,9 @@
     <t>CODEMGE</t>
   </si>
   <si>
-    <t>Companhia de Desenvolvimento de Minas Gerais</t>
-  </si>
-  <si>
     <t>COHAB</t>
   </si>
   <si>
-    <t>Companhia de Habitação do Estado de Minas Gerais</t>
-  </si>
-  <si>
     <t>DEER</t>
   </si>
   <si>
@@ -193,9 +187,6 @@
     <t>HPM</t>
   </si>
   <si>
-    <t>Hospital da Polícia Militar de Minas Gerais</t>
-  </si>
-  <si>
     <t>IDENE</t>
   </si>
   <si>
@@ -452,6 +443,15 @@
   </si>
   <si>
     <t>DMAES PONTE NOVA</t>
+  </si>
+  <si>
+    <t>para_codigo</t>
+  </si>
+  <si>
+    <t>PMMG</t>
+  </si>
+  <si>
+    <t>Polícia Militar do Estado de Minas Gerais - HPM</t>
   </si>
 </sst>
 </file>
@@ -935,11 +935,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1261,17 +1262,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C71"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="73.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="20.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1279,8 +1280,11 @@
       <c r="C1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1290,8 +1294,11 @@
       <c r="C2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2">
+        <v>2431</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1301,8 +1308,11 @@
       <c r="C3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1312,8 +1322,11 @@
       <c r="C4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4">
+        <v>2461</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1323,8 +1336,11 @@
       <c r="C5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5">
+        <v>2441</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -1334,8 +1350,11 @@
       <c r="C6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6">
+        <v>2471</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1345,8 +1364,11 @@
       <c r="C7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -1356,703 +1378,895 @@
       <c r="C8" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8">
+        <v>1521</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" t="s">
+        <v>130</v>
+      </c>
+      <c r="D9" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>18</v>
       </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
+        <v>130</v>
+      </c>
+      <c r="C10" t="s">
+        <v>130</v>
+      </c>
+      <c r="D10" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>132</v>
+      </c>
+      <c r="B11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C11" t="s">
+        <v>130</v>
+      </c>
+      <c r="D11" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>19</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B12" t="s">
         <v>20</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C12" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>135</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="D12">
+        <v>2301</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>134</v>
+      </c>
+      <c r="B13" t="s">
+        <v>130</v>
+      </c>
+      <c r="C13" t="s">
+        <v>130</v>
+      </c>
+      <c r="D13" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B14" t="s">
+        <v>130</v>
+      </c>
+      <c r="C14" t="s">
+        <v>130</v>
+      </c>
+      <c r="D14" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15">
+        <v>3051</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18">
+        <v>2071</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19">
+        <v>2181</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20">
+        <v>2091</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21">
+        <v>2271</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22">
+        <v>2061</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23">
+        <v>2161</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" t="s">
+        <v>35</v>
+      </c>
+      <c r="D24">
+        <v>4091</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B25" t="s">
+        <v>130</v>
+      </c>
+      <c r="C25" t="s">
+        <v>130</v>
+      </c>
+      <c r="D25" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B26" t="s">
+        <v>130</v>
+      </c>
+      <c r="C26" t="s">
+        <v>130</v>
+      </c>
+      <c r="D26" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" t="s">
+        <v>42</v>
+      </c>
+      <c r="D27">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29">
+        <v>2321</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30" t="s">
+        <v>137</v>
+      </c>
+      <c r="C30" t="s">
+        <v>136</v>
+      </c>
+      <c r="D30">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>49</v>
+      </c>
+      <c r="B31" t="s">
+        <v>50</v>
+      </c>
+      <c r="C31" t="s">
+        <v>49</v>
+      </c>
+      <c r="D31">
+        <v>2421</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>51</v>
+      </c>
+      <c r="B32" t="s">
+        <v>52</v>
+      </c>
+      <c r="C32" t="s">
+        <v>51</v>
+      </c>
+      <c r="D32">
+        <v>2101</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>53</v>
+      </c>
+      <c r="B33" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" t="s">
+        <v>53</v>
+      </c>
+      <c r="D33">
+        <v>2201</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>55</v>
+      </c>
+      <c r="B34" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34" t="s">
+        <v>55</v>
+      </c>
+      <c r="D34">
+        <v>2241</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>57</v>
+      </c>
+      <c r="B35" t="s">
+        <v>58</v>
+      </c>
+      <c r="C35" t="s">
+        <v>57</v>
+      </c>
+      <c r="D35">
+        <v>2371</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>59</v>
+      </c>
+      <c r="B36" t="s">
+        <v>60</v>
+      </c>
+      <c r="C36" t="s">
+        <v>61</v>
+      </c>
+      <c r="D36">
+        <v>5131</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>62</v>
+      </c>
+      <c r="B37" t="s">
+        <v>63</v>
+      </c>
+      <c r="C37" t="s">
+        <v>62</v>
+      </c>
+      <c r="D37">
+        <v>2331</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>64</v>
+      </c>
+      <c r="B38" t="s">
+        <v>65</v>
+      </c>
+      <c r="C38" t="s">
+        <v>64</v>
+      </c>
+      <c r="D38">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>66</v>
+      </c>
+      <c r="B39" t="s">
+        <v>67</v>
+      </c>
+      <c r="C39" t="s">
+        <v>66</v>
+      </c>
+      <c r="D39">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B40" t="s">
+        <v>69</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D40" s="1">
+        <v>2251</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>70</v>
+      </c>
+      <c r="B41" t="s">
+        <v>71</v>
+      </c>
+      <c r="C41" t="s">
+        <v>70</v>
+      </c>
+      <c r="D41">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B42" t="s">
+        <v>73</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D42" s="1">
+        <v>5191</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B43" t="s">
+        <v>130</v>
+      </c>
+      <c r="C43" t="s">
+        <v>130</v>
+      </c>
+      <c r="D43" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B44" t="s">
+        <v>130</v>
+      </c>
+      <c r="C44" t="s">
+        <v>130</v>
+      </c>
+      <c r="D44" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>74</v>
+      </c>
+      <c r="B45" t="s">
+        <v>75</v>
+      </c>
+      <c r="C45" t="s">
+        <v>74</v>
+      </c>
+      <c r="D45">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>76</v>
+      </c>
+      <c r="B46" t="s">
+        <v>77</v>
+      </c>
+      <c r="C46" t="s">
+        <v>76</v>
+      </c>
+      <c r="D46">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>78</v>
+      </c>
+      <c r="B47" t="s">
+        <v>79</v>
+      </c>
+      <c r="C47" t="s">
+        <v>80</v>
+      </c>
+      <c r="D47">
+        <v>5141</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B48" t="s">
+        <v>130</v>
+      </c>
+      <c r="C48" t="s">
+        <v>130</v>
+      </c>
+      <c r="D48" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B49" t="s">
+        <v>130</v>
+      </c>
+      <c r="C49" t="s">
+        <v>130</v>
+      </c>
+      <c r="D49" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B50" t="s">
+        <v>82</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D50" s="1">
+        <v>5151</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>83</v>
+      </c>
+      <c r="B51" t="s">
+        <v>84</v>
+      </c>
+      <c r="C51" t="s">
+        <v>83</v>
+      </c>
+      <c r="D51" s="2">
+        <v>1721</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>85</v>
+      </c>
+      <c r="B52" t="s">
+        <v>86</v>
+      </c>
+      <c r="C52" t="s">
+        <v>85</v>
+      </c>
+      <c r="D52">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>87</v>
+      </c>
+      <c r="B53" t="s">
+        <v>88</v>
+      </c>
+      <c r="C53" t="s">
+        <v>87</v>
+      </c>
+      <c r="D53">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>89</v>
+      </c>
+      <c r="B54" t="s">
+        <v>90</v>
+      </c>
+      <c r="C54" t="s">
+        <v>89</v>
+      </c>
+      <c r="D54" s="2">
+        <v>1711</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
         <v>133</v>
       </c>
-      <c r="C11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B13" t="s">
-        <v>133</v>
-      </c>
-      <c r="C13" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23" t="s">
-        <v>36</v>
-      </c>
-      <c r="C23" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B24" t="s">
-        <v>133</v>
-      </c>
-      <c r="C24" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B25" t="s">
-        <v>133</v>
-      </c>
-      <c r="C25" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>44</v>
-      </c>
-      <c r="B26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>46</v>
-      </c>
-      <c r="B27" t="s">
-        <v>47</v>
-      </c>
-      <c r="C27" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>48</v>
-      </c>
-      <c r="B28" t="s">
-        <v>49</v>
-      </c>
-      <c r="C28" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>50</v>
-      </c>
-      <c r="B29" t="s">
-        <v>51</v>
-      </c>
-      <c r="C29" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>52</v>
-      </c>
-      <c r="B30" t="s">
-        <v>53</v>
-      </c>
-      <c r="C30" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>54</v>
-      </c>
-      <c r="B31" t="s">
-        <v>55</v>
-      </c>
-      <c r="C31" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>56</v>
-      </c>
-      <c r="B32" t="s">
-        <v>57</v>
-      </c>
-      <c r="C32" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>58</v>
-      </c>
-      <c r="B33" t="s">
-        <v>59</v>
-      </c>
-      <c r="C33" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>60</v>
-      </c>
-      <c r="B34" t="s">
-        <v>61</v>
-      </c>
-      <c r="C34" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>62</v>
-      </c>
-      <c r="B35" t="s">
-        <v>63</v>
-      </c>
-      <c r="C35" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>65</v>
-      </c>
-      <c r="B36" t="s">
-        <v>66</v>
-      </c>
-      <c r="C36" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>67</v>
-      </c>
-      <c r="B37" t="s">
-        <v>68</v>
-      </c>
-      <c r="C37" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>69</v>
-      </c>
-      <c r="B38" t="s">
-        <v>70</v>
-      </c>
-      <c r="C38" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B39" t="s">
-        <v>72</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>73</v>
-      </c>
-      <c r="B40" t="s">
-        <v>74</v>
-      </c>
-      <c r="C40" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B41" t="s">
-        <v>133</v>
-      </c>
-      <c r="C41" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
+      <c r="B55" t="s">
+        <v>92</v>
+      </c>
+      <c r="C55" t="s">
+        <v>91</v>
+      </c>
+      <c r="D55" s="2">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>93</v>
+      </c>
+      <c r="B56" t="s">
+        <v>94</v>
+      </c>
+      <c r="C56" t="s">
+        <v>93</v>
+      </c>
+      <c r="D56">
+        <v>1481</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>95</v>
+      </c>
+      <c r="B57" t="s">
+        <v>96</v>
+      </c>
+      <c r="C57" t="s">
+        <v>95</v>
+      </c>
+      <c r="D57">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>97</v>
+      </c>
+      <c r="B58" t="s">
+        <v>98</v>
+      </c>
+      <c r="C58" t="s">
+        <v>97</v>
+      </c>
+      <c r="D58">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>99</v>
+      </c>
+      <c r="B59" t="s">
+        <v>100</v>
+      </c>
+      <c r="C59" t="s">
+        <v>99</v>
+      </c>
+      <c r="D59">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>101</v>
+      </c>
+      <c r="B60" t="s">
+        <v>102</v>
+      </c>
+      <c r="C60" t="s">
+        <v>101</v>
+      </c>
+      <c r="D60">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>103</v>
+      </c>
+      <c r="B61" t="s">
+        <v>104</v>
+      </c>
+      <c r="C61" t="s">
+        <v>103</v>
+      </c>
+      <c r="D61">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>105</v>
+      </c>
+      <c r="B62" t="s">
+        <v>106</v>
+      </c>
+      <c r="C62" t="s">
+        <v>105</v>
+      </c>
+      <c r="D62">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>107</v>
+      </c>
+      <c r="B63" t="s">
+        <v>108</v>
+      </c>
+      <c r="C63" t="s">
+        <v>107</v>
+      </c>
+      <c r="D63">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>109</v>
+      </c>
+      <c r="B64" t="s">
+        <v>110</v>
+      </c>
+      <c r="C64" t="s">
+        <v>109</v>
+      </c>
+      <c r="D64">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>111</v>
+      </c>
+      <c r="B65" t="s">
+        <v>112</v>
+      </c>
+      <c r="C65" t="s">
+        <v>111</v>
+      </c>
+      <c r="D65">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>113</v>
+      </c>
+      <c r="B66" t="s">
+        <v>114</v>
+      </c>
+      <c r="C66" t="s">
+        <v>113</v>
+      </c>
+      <c r="D66" s="2">
+        <v>1631</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B42" t="s">
-        <v>133</v>
-      </c>
-      <c r="C42" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B43" t="s">
-        <v>76</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>77</v>
-      </c>
-      <c r="B44" t="s">
-        <v>78</v>
-      </c>
-      <c r="C44" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>79</v>
-      </c>
-      <c r="B45" t="s">
-        <v>80</v>
-      </c>
-      <c r="C45" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B46" t="s">
-        <v>133</v>
-      </c>
-      <c r="C46" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B47" t="s">
-        <v>133</v>
-      </c>
-      <c r="C47" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>81</v>
-      </c>
-      <c r="B48" t="s">
+      <c r="B67" t="s">
+        <v>130</v>
+      </c>
+      <c r="C67" t="s">
+        <v>130</v>
+      </c>
+      <c r="D67" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>115</v>
+      </c>
+      <c r="B68" t="s">
         <v>82</v>
       </c>
-      <c r="C48" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B49" t="s">
-        <v>85</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>86</v>
-      </c>
-      <c r="B50" t="s">
-        <v>87</v>
-      </c>
-      <c r="C50" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>88</v>
-      </c>
-      <c r="B51" t="s">
-        <v>89</v>
-      </c>
-      <c r="C51" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>90</v>
-      </c>
-      <c r="B52" t="s">
-        <v>91</v>
-      </c>
-      <c r="C52" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>92</v>
-      </c>
-      <c r="B53" t="s">
-        <v>93</v>
-      </c>
-      <c r="C53" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>136</v>
-      </c>
-      <c r="B54" t="s">
-        <v>95</v>
-      </c>
-      <c r="C54" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>96</v>
-      </c>
-      <c r="B55" t="s">
-        <v>97</v>
-      </c>
-      <c r="C55" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>98</v>
-      </c>
-      <c r="B56" t="s">
-        <v>99</v>
-      </c>
-      <c r="C56" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>100</v>
-      </c>
-      <c r="B57" t="s">
-        <v>101</v>
-      </c>
-      <c r="C57" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>102</v>
-      </c>
-      <c r="B58" t="s">
-        <v>103</v>
-      </c>
-      <c r="C58" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>104</v>
-      </c>
-      <c r="B59" t="s">
-        <v>105</v>
-      </c>
-      <c r="C59" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>106</v>
-      </c>
-      <c r="B60" t="s">
-        <v>107</v>
-      </c>
-      <c r="C60" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>108</v>
-      </c>
-      <c r="B61" t="s">
-        <v>109</v>
-      </c>
-      <c r="C61" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>110</v>
-      </c>
-      <c r="B62" t="s">
-        <v>111</v>
-      </c>
-      <c r="C62" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>112</v>
-      </c>
-      <c r="B63" t="s">
-        <v>113</v>
-      </c>
-      <c r="C63" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>114</v>
-      </c>
-      <c r="B64" t="s">
+      <c r="C68" t="s">
         <v>115</v>
       </c>
-      <c r="C64" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+      <c r="D68">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
         <v>116</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B69" t="s">
         <v>117</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C69" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B66" t="s">
-        <v>133</v>
-      </c>
-      <c r="C66" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+      <c r="D69">
+        <v>2351</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
         <v>118</v>
       </c>
-      <c r="B67" t="s">
-        <v>85</v>
-      </c>
-      <c r="C67" t="s">
+      <c r="B70" t="s">
+        <v>119</v>
+      </c>
+      <c r="C70" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>119</v>
-      </c>
-      <c r="B68" t="s">
+      <c r="D70">
+        <v>2311</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
         <v>120</v>
       </c>
-      <c r="C68" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+      <c r="B71" t="s">
         <v>121</v>
       </c>
-      <c r="B69" t="s">
-        <v>122</v>
-      </c>
-      <c r="C69" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>123</v>
-      </c>
-      <c r="B70" t="s">
-        <v>124</v>
-      </c>
-      <c r="C70" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>137</v>
-      </c>
-      <c r="B71" t="s">
-        <v>133</v>
-      </c>
       <c r="C71" t="s">
-        <v>133</v>
+        <v>120</v>
+      </c>
+      <c r="D71">
+        <v>2281</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C1">
-    <sortState ref="A2:C61">
+  <autoFilter ref="A1:D1">
+    <sortState ref="A2:D71">
       <sortCondition ref="A1"/>
     </sortState>
   </autoFilter>

--- a/de_para_orgao.xlsx
+++ b/de_para_orgao.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="141">
   <si>
     <t>para_orgao</t>
   </si>
@@ -452,6 +452,15 @@
   </si>
   <si>
     <t>Polícia Militar do Estado de Minas Gerais - HPM</t>
+  </si>
+  <si>
+    <t>DETRAN MG</t>
+  </si>
+  <si>
+    <t>Departamento Estadual de Trânsito de Minas Gerais</t>
+  </si>
+  <si>
+    <t>DETRAN</t>
   </si>
 </sst>
 </file>
@@ -1262,7 +1271,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.85546875" bestFit="1" customWidth="1"/>
@@ -1440,511 +1449,511 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B13" t="s">
+        <v>139</v>
+      </c>
+      <c r="C13" t="s">
+        <v>140</v>
+      </c>
+      <c r="D13">
+        <v>2481</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>134</v>
       </c>
-      <c r="B13" t="s">
-        <v>130</v>
-      </c>
-      <c r="C13" t="s">
-        <v>130</v>
-      </c>
-      <c r="D13" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="B14" t="s">
+        <v>130</v>
+      </c>
+      <c r="C14" t="s">
+        <v>130</v>
+      </c>
+      <c r="D14" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B14" t="s">
-        <v>130</v>
-      </c>
-      <c r="C14" t="s">
-        <v>130</v>
-      </c>
-      <c r="D14" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>21</v>
-      </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>130</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15">
-        <v>3051</v>
+        <v>130</v>
+      </c>
+      <c r="D15" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D16">
-        <v>1541</v>
+        <v>3051</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D17">
-        <v>2171</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D18">
-        <v>2071</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D19">
-        <v>2181</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D20">
-        <v>2091</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C21" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D21">
-        <v>2271</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C22" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D22">
-        <v>2061</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D23">
-        <v>2161</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" t="s">
+        <v>40</v>
+      </c>
+      <c r="D24">
+        <v>2161</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>33</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B25" t="s">
         <v>34</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C25" t="s">
         <v>35</v>
       </c>
-      <c r="D24">
+      <c r="D25">
         <v>4091</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B25" t="s">
-        <v>130</v>
-      </c>
-      <c r="C25" t="s">
-        <v>130</v>
-      </c>
-      <c r="D25" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B26" t="s">
+        <v>130</v>
+      </c>
+      <c r="C26" t="s">
+        <v>130</v>
+      </c>
+      <c r="D26" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B26" t="s">
-        <v>130</v>
-      </c>
-      <c r="C26" t="s">
-        <v>130</v>
-      </c>
-      <c r="D26" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>42</v>
-      </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>130</v>
       </c>
       <c r="C27" t="s">
-        <v>42</v>
-      </c>
-      <c r="D27">
-        <v>2261</v>
+        <v>130</v>
+      </c>
+      <c r="D27" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D28">
-        <v>1071</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D29">
-        <v>2321</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B30" t="s">
-        <v>137</v>
+        <v>47</v>
       </c>
       <c r="C30" t="s">
-        <v>136</v>
+        <v>46</v>
       </c>
       <c r="D30">
-        <v>1251</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B31" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="C31" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="D31">
-        <v>2421</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B32" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D32">
-        <v>2101</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B33" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C33" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D33">
-        <v>2201</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B34" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C34" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D34">
-        <v>2241</v>
+        <v>2201</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B35" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C35" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D35">
-        <v>2371</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B36" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C36" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D36">
-        <v>5131</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B37" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C37" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D37">
-        <v>2331</v>
+        <v>5131</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B38" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C38" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D38">
-        <v>2011</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>64</v>
+      </c>
+      <c r="B39" t="s">
+        <v>65</v>
+      </c>
+      <c r="C39" t="s">
+        <v>64</v>
+      </c>
+      <c r="D39">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>66</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B40" t="s">
         <v>67</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C40" t="s">
         <v>66</v>
       </c>
-      <c r="D39">
+      <c r="D40">
         <v>2121</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B41" t="s">
         <v>69</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C41" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D40" s="1">
+      <c r="D41" s="1">
         <v>2251</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>70</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B42" t="s">
         <v>71</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C42" t="s">
         <v>70</v>
       </c>
-      <c r="D41">
+      <c r="D42">
         <v>2041</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B42" t="s">
-        <v>73</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D42" s="1">
-        <v>5191</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
       <c r="B43" t="s">
-        <v>130</v>
-      </c>
-      <c r="C43" t="s">
-        <v>130</v>
-      </c>
-      <c r="D43" t="s">
-        <v>130</v>
+        <v>73</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D43" s="1">
+        <v>5191</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B44" t="s">
+        <v>130</v>
+      </c>
+      <c r="C44" t="s">
+        <v>130</v>
+      </c>
+      <c r="D44" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B44" t="s">
-        <v>130</v>
-      </c>
-      <c r="C44" t="s">
-        <v>130</v>
-      </c>
-      <c r="D44" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>74</v>
-      </c>
       <c r="B45" t="s">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="C45" t="s">
-        <v>74</v>
-      </c>
-      <c r="D45">
-        <v>1101</v>
+        <v>130</v>
+      </c>
+      <c r="D45" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B46" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C46" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D46">
-        <v>1511</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>76</v>
+      </c>
+      <c r="B47" t="s">
+        <v>77</v>
+      </c>
+      <c r="C47" t="s">
+        <v>76</v>
+      </c>
+      <c r="D47">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>78</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B48" t="s">
         <v>79</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C48" t="s">
         <v>80</v>
       </c>
-      <c r="D47">
+      <c r="D48">
         <v>5141</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B48" t="s">
-        <v>130</v>
-      </c>
-      <c r="C48" t="s">
-        <v>130</v>
-      </c>
-      <c r="D48" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B49" t="s">
         <v>130</v>
@@ -1958,209 +1967,209 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B50" t="s">
+        <v>130</v>
+      </c>
+      <c r="C50" t="s">
+        <v>130</v>
+      </c>
+      <c r="D50" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B51" t="s">
         <v>82</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C51" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D50" s="1">
+      <c r="D51" s="1">
         <v>5151</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>83</v>
-      </c>
-      <c r="B51" t="s">
-        <v>84</v>
-      </c>
-      <c r="C51" t="s">
-        <v>83</v>
-      </c>
-      <c r="D51" s="2">
-        <v>1721</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B52" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C52" t="s">
-        <v>85</v>
-      </c>
-      <c r="D52">
-        <v>1231</v>
+        <v>83</v>
+      </c>
+      <c r="D52" s="2">
+        <v>1721</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B53" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C53" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D53">
-        <v>1271</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B54" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C54" t="s">
-        <v>89</v>
-      </c>
-      <c r="D54" s="2">
-        <v>1711</v>
+        <v>87</v>
+      </c>
+      <c r="D54">
+        <v>1271</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>133</v>
+        <v>89</v>
       </c>
       <c r="B55" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C55" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D55" s="2">
-        <v>1221</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="B56" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C56" t="s">
-        <v>93</v>
-      </c>
-      <c r="D56">
-        <v>1481</v>
+        <v>91</v>
+      </c>
+      <c r="D56" s="2">
+        <v>1221</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B57" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C57" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D57">
-        <v>1261</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B58" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C58" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D58">
-        <v>1191</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B59" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C59" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D59">
-        <v>1491</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B60" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C60" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D60">
-        <v>1301</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B61" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C61" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D61">
-        <v>1451</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B62" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C62" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D62">
-        <v>1371</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B63" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C63" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D63">
-        <v>1501</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B64" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C64" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D64">
         <v>1501</v>
@@ -2168,105 +2177,119 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B65" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C65" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D65">
-        <v>1321</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>111</v>
+      </c>
+      <c r="B66" t="s">
+        <v>112</v>
+      </c>
+      <c r="C66" t="s">
+        <v>111</v>
+      </c>
+      <c r="D66">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
         <v>113</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B67" t="s">
         <v>114</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C67" t="s">
         <v>113</v>
       </c>
-      <c r="D66" s="2">
+      <c r="D67" s="2">
         <v>1631</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B67" t="s">
-        <v>130</v>
-      </c>
-      <c r="C67" t="s">
-        <v>130</v>
-      </c>
-      <c r="D67" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>115</v>
-      </c>
       <c r="B68" t="s">
-        <v>82</v>
+        <v>130</v>
       </c>
       <c r="C68" t="s">
-        <v>115</v>
-      </c>
-      <c r="D68">
-        <v>2211</v>
+        <v>130</v>
+      </c>
+      <c r="D68" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B69" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="C69" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D69">
-        <v>2351</v>
+        <v>2211</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B70" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C70" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D70">
-        <v>2311</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>118</v>
+      </c>
+      <c r="B71" t="s">
+        <v>119</v>
+      </c>
+      <c r="C71" t="s">
+        <v>118</v>
+      </c>
+      <c r="D71">
+        <v>2311</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
         <v>120</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B72" t="s">
         <v>121</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C72" t="s">
         <v>120</v>
       </c>
-      <c r="D71">
+      <c r="D72">
         <v>2281</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1">
-    <sortState ref="A2:D71">
+    <sortState ref="A2:D72">
       <sortCondition ref="A1"/>
     </sortState>
   </autoFilter>
